--- a/data/trans_orig/P57C2_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P57C2_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se ha sentido bien consigo mismo/a en 2023</t>
+          <t>Población según si se ha sentido bien consigo mismo/a en 2023 (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7805</t>
+          <t>7727</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24813</t>
+          <t>23968</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12114</t>
+          <t>11697</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24982</t>
+          <t>23905</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22422</t>
+          <t>22435</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42477</t>
+          <t>43914</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27205</t>
+          <t>27177</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47482</t>
+          <t>46604</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>61546</t>
+          <t>61973</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>85469</t>
+          <t>84783</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>94386</t>
+          <t>94796</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>126372</t>
+          <t>127178</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>81617</t>
+          <t>81372</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>113964</t>
+          <t>112684</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>153434</t>
+          <t>152521</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>187334</t>
+          <t>187080</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>241874</t>
+          <t>242226</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>286104</t>
+          <t>288775</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,88%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>202080</t>
+          <t>199792</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>243585</t>
+          <t>242237</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>307908</t>
+          <t>305133</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>347142</t>
+          <t>346325</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>522607</t>
+          <t>519633</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>580164</t>
+          <t>580236</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>45,97%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>128497</t>
+          <t>128142</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>166295</t>
+          <t>165290</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>142347</t>
+          <t>144230</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>181335</t>
+          <t>182358</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>281408</t>
+          <t>282348</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>333835</t>
+          <t>338637</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,83%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10514</t>
+          <t>9794</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28048</t>
+          <t>28038</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16383</t>
+          <t>16807</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40172</t>
+          <t>42092</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31716</t>
+          <t>32601</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61301</t>
+          <t>64673</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31809</t>
+          <t>29518</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>64014</t>
+          <t>63059</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>41781</t>
+          <t>42607</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>74962</t>
+          <t>74790</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>81726</t>
+          <t>79792</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>128194</t>
+          <t>128989</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>103681</t>
+          <t>107891</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>182499</t>
+          <t>182240</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>124692</t>
+          <t>127753</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>208948</t>
+          <t>209007</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>262720</t>
+          <t>263714</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>373055</t>
+          <t>383199</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>701473</t>
+          <t>697509</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1127691</t>
+          <t>1123380</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1042318</t>
+          <t>1042907</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1468704</t>
+          <t>1454016</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>65,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1870240</t>
+          <t>1838531</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2456981</t>
+          <t>2455899</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>54,28%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>921597</t>
+          <t>924824</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1431646</t>
+          <t>1465156</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>575153</t>
+          <t>595935</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>925514</t>
+          <t>925058</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1631385</t>
+          <t>1626551</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2279140</t>
+          <t>2309238</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>51,04%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>3098</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17704</t>
+          <t>17692</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>494</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4644</t>
+          <t>4954</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4559</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17863</t>
+          <t>20909</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4889</t>
+          <t>5228</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21673</t>
+          <t>23887</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6901</t>
+          <t>6675</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20017</t>
+          <t>20518</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14582</t>
+          <t>14523</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35251</t>
+          <t>35890</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21542</t>
+          <t>22809</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>46001</t>
+          <t>46246</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>25597</t>
+          <t>25757</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>47262</t>
+          <t>45657</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>53050</t>
+          <t>52821</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>86544</t>
+          <t>84947</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>252199</t>
+          <t>257000</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>307585</t>
+          <t>309690</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>300880</t>
+          <t>298673</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>346223</t>
+          <t>345790</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>570391</t>
+          <t>569026</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>639809</t>
+          <t>642407</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>49,17%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>286871</t>
+          <t>285743</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>344096</t>
+          <t>340462</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>52,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>265664</t>
+          <t>265503</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>310777</t>
+          <t>310938</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>566885</t>
+          <t>566453</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>636372</t>
+          <t>639547</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>48,95%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27748</t>
+          <t>28134</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>56686</t>
+          <t>55614</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>33692</t>
+          <t>33952</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>61423</t>
+          <t>62834</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>68892</t>
+          <t>66761</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>107772</t>
+          <t>108950</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>70976</t>
+          <t>71432</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>114995</t>
+          <t>114005</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>116531</t>
+          <t>115501</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>164249</t>
+          <t>164391</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>203085</t>
+          <t>200707</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>270539</t>
+          <t>265689</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>212480</t>
+          <t>217789</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>317273</t>
+          <t>316899</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>307045</t>
+          <t>306157</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>421527</t>
+          <t>424061</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>576204</t>
+          <t>563590</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>721287</t>
+          <t>719079</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,14%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1194718</t>
+          <t>1142221</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1633344</t>
+          <t>1635217</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1690486</t>
+          <t>1694332</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2187969</t>
+          <t>2211313</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2965808</t>
+          <t>3006226</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3635674</t>
+          <t>3627736</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>51,14%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1373127</t>
+          <t>1373392</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1929223</t>
+          <t>1987557</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1007647</t>
+          <t>1015030</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1369594</t>
+          <t>1370691</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2538113</t>
+          <t>2527489</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3323987</t>
+          <t>3271572</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>46,12%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57C2_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P57C2_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>13627</t>
+          <t>14551</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7727</t>
+          <t>7882</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23968</t>
+          <t>25082</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>17648</t>
+          <t>19104</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11697</t>
+          <t>13286</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23905</t>
+          <t>26879</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>31276</t>
+          <t>33655</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22435</t>
+          <t>24603</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43914</t>
+          <t>45786</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>35765</t>
+          <t>39443</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27177</t>
+          <t>30679</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46604</t>
+          <t>50705</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>72785</t>
+          <t>81869</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>61973</t>
+          <t>69108</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>84783</t>
+          <t>95724</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>108550</t>
+          <t>121312</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>94796</t>
+          <t>104721</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>127178</t>
+          <t>138537</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,95%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>94496</t>
+          <t>110012</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>81372</t>
+          <t>91571</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>112684</t>
+          <t>129594</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>170336</t>
+          <t>187292</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>152521</t>
+          <t>168242</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>187080</t>
+          <t>205371</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>264831</t>
+          <t>297305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>242226</t>
+          <t>275730</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>288775</t>
+          <t>326020</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,42%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>222937</t>
+          <t>244938</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>199792</t>
+          <t>223925</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>242237</t>
+          <t>269217</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>326870</t>
+          <t>356568</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>305133</t>
+          <t>335616</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>346325</t>
+          <t>379590</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>549807</t>
+          <t>601506</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>519633</t>
+          <t>569239</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>580236</t>
+          <t>635036</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>45,62%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>146523</t>
+          <t>167925</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>128142</t>
+          <t>146543</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>165290</t>
+          <t>189675</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>161350</t>
+          <t>170350</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>144230</t>
+          <t>153120</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>182358</t>
+          <t>188991</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>307873</t>
+          <t>338276</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>282348</t>
+          <t>310255</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>338637</t>
+          <t>366233</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,31%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>513348</t>
+          <t>576870</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>513348</t>
+          <t>576870</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>513348</t>
+          <t>576870</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>748989</t>
+          <t>815184</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>748989</t>
+          <t>815184</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>748989</t>
+          <t>815184</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1262337</t>
+          <t>1392054</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1262337</t>
+          <t>1392054</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1262337</t>
+          <t>1392054</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>17633</t>
+          <t>18785</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9794</t>
+          <t>12021</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28038</t>
+          <t>29605</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>27022</t>
+          <t>30667</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16807</t>
+          <t>20390</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42092</t>
+          <t>45347</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>44655</t>
+          <t>49452</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32601</t>
+          <t>35728</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64673</t>
+          <t>66605</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>46998</t>
+          <t>50271</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29518</t>
+          <t>38718</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>63059</t>
+          <t>67506</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>58131</t>
+          <t>68907</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>42607</t>
+          <t>55521</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>74790</t>
+          <t>84261</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>105129</t>
+          <t>119179</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>79792</t>
+          <t>99116</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>128989</t>
+          <t>140683</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>149584</t>
+          <t>162535</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>107891</t>
+          <t>137383</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>182240</t>
+          <t>189430</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>177223</t>
+          <t>201741</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>127753</t>
+          <t>179257</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>209007</t>
+          <t>228416</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>326808</t>
+          <t>364276</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>263714</t>
+          <t>327677</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>383199</t>
+          <t>400097</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>989300</t>
+          <t>1054721</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>697509</t>
+          <t>1002375</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1123380</t>
+          <t>1108507</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>49,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1183499</t>
+          <t>1052043</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1042907</t>
+          <t>1007858</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1454016</t>
+          <t>1095532</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2172800</t>
+          <t>2106764</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1838531</t>
+          <t>2033613</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2455899</t>
+          <t>2167922</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>49,29%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1085180</t>
+          <t>942720</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>924824</t>
+          <t>888637</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1465156</t>
+          <t>994347</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>790093</t>
+          <t>816183</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>595935</t>
+          <t>772635</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>925058</t>
+          <t>857653</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1875274</t>
+          <t>1758903</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1626551</t>
+          <t>1691270</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2309238</t>
+          <t>1826549</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>41,53%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2288695</t>
+          <t>2229032</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2288695</t>
+          <t>2229032</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2288695</t>
+          <t>2229032</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2235969</t>
+          <t>2169541</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2235969</t>
+          <t>2169541</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2235969</t>
+          <t>2169541</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>4524665</t>
+          <t>4398574</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4524665</t>
+          <t>4398574</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4524665</t>
+          <t>4398574</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>8151</t>
+          <t>9708</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3098</t>
+          <t>3866</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17692</t>
+          <t>19583</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,17 +2124,17 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1615</t>
+          <t>1736</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>500</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4954</t>
+          <t>5118</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,22 +2159,22 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>9765</t>
+          <t>11444</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>5546</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20909</t>
+          <t>22437</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10596</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5228</t>
+          <t>5465</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23887</t>
+          <t>22198</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>12200</t>
+          <t>12747</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6675</t>
+          <t>7030</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20518</t>
+          <t>21764</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>22796</t>
+          <t>23410</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14523</t>
+          <t>15633</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35890</t>
+          <t>37398</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>32209</t>
+          <t>36671</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22809</t>
+          <t>25746</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>46246</t>
+          <t>50688</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>34847</t>
+          <t>39082</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>25757</t>
+          <t>29130</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>45657</t>
+          <t>51352</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>67056</t>
+          <t>75753</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>52821</t>
+          <t>59541</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>84947</t>
+          <t>94195</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>282123</t>
+          <t>308627</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>257000</t>
+          <t>280372</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>309690</t>
+          <t>339204</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>323612</t>
+          <t>352472</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>298673</t>
+          <t>327531</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>345790</t>
+          <t>377365</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>605735</t>
+          <t>661100</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>569026</t>
+          <t>625706</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>642407</t>
+          <t>701565</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>48,52%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>312905</t>
+          <t>345308</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>285743</t>
+          <t>317046</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>340462</t>
+          <t>377011</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>53,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>288188</t>
+          <t>328839</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>265503</t>
+          <t>304257</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>310938</t>
+          <t>354509</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>44,75%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>601093</t>
+          <t>674147</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>566453</t>
+          <t>637356</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>639547</t>
+          <t>712293</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>49,26%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>645983</t>
+          <t>710977</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>645983</t>
+          <t>710977</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>645983</t>
+          <t>710977</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1306445</t>
+          <t>1445854</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1306445</t>
+          <t>1445854</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1306445</t>
+          <t>1445854</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>39411</t>
+          <t>43043</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28134</t>
+          <t>30458</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>55614</t>
+          <t>58685</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>46285</t>
+          <t>51507</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>33952</t>
+          <t>38729</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>62834</t>
+          <t>68425</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>85695</t>
+          <t>94551</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>66761</t>
+          <t>76571</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>108950</t>
+          <t>116047</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>93358</t>
+          <t>100378</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>71432</t>
+          <t>82330</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>114005</t>
+          <t>122270</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>143117</t>
+          <t>163523</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>115501</t>
+          <t>144813</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>164391</t>
+          <t>187061</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>236475</t>
+          <t>263901</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>200707</t>
+          <t>234919</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>265689</t>
+          <t>292455</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>276289</t>
+          <t>309218</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>217789</t>
+          <t>276451</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>316899</t>
+          <t>348619</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>382406</t>
+          <t>428116</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>306157</t>
+          <t>391962</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>424061</t>
+          <t>461657</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>658695</t>
+          <t>737334</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>563590</t>
+          <t>694359</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>719079</t>
+          <t>787658</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,88%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1494360</t>
+          <t>1608287</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1142221</t>
+          <t>1544650</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1635217</t>
+          <t>1675897</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>47,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1833982</t>
+          <t>1761083</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1694332</t>
+          <t>1706622</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2211313</t>
+          <t>1817415</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>47,35%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>48,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>3328341</t>
+          <t>3369370</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3006226</t>
+          <t>3286538</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3627736</t>
+          <t>3457921</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>47,78%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1544608</t>
+          <t>1455953</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1373392</t>
+          <t>1389705</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1987557</t>
+          <t>1521673</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1239632</t>
+          <t>1315373</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1015030</t>
+          <t>1263235</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1370691</t>
+          <t>1374140</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>2784240</t>
+          <t>2771326</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2527489</t>
+          <t>2678053</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3271572</t>
+          <t>2851095</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>39,4%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3448026</t>
+          <t>3516879</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3448026</t>
+          <t>3516879</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3448026</t>
+          <t>3516879</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3645421</t>
+          <t>3719603</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3645421</t>
+          <t>3719603</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3645421</t>
+          <t>3719603</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7093447</t>
+          <t>7236482</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7093447</t>
+          <t>7236482</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7093447</t>
+          <t>7236482</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
